--- a/JsonConverter/ExcelFiles/WJWaveEnemy.xlsx
+++ b/JsonConverter/ExcelFiles/WJWaveEnemy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15647C32-E4B8-4402-9370-1AD2366F47FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BB6069-59C6-4516-96B3-27BE06FD5CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31140" yWindow="2340" windowWidth="21270" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34290" yWindow="3435" windowWidth="22485" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_WaveEnemy" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>(name)</t>
   </si>
@@ -48,15 +48,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>2,3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Unit_Enemy_1,Unit_Enemy_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>WaveEnemy_1_2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -69,6 +61,37 @@
   </si>
   <si>
     <t>EnemyMaxCountList</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WaveEnemy_2_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WaveEnemy_2_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WaveEnemy_3_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WaveEnemy_3_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit_Enemy_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WaveEnemy_1_2</t>
+  </si>
+  <si>
+    <t>30,5</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,20</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -155,7 +178,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -178,23 +201,204 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -207,6 +411,45 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -429,7 +672,7 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -445,242 +688,266 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A4" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="20">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A5" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="17">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A7" s="14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4">
-        <v>5</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="C7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="A8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="13">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="16">
+        <v>60</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
